--- a/成本配置模板.xlsx
+++ b/成本配置模板.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="32065" windowHeight="14605" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="使用说明" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,35 +16,201 @@
     <sheet name="其他成本" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="25">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -54,26 +219,216 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FF70AD47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -83,48 +438,339 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00A9D18E"/>
+        <color rgb="FFA9D18E"/>
       </left>
       <right style="thin">
-        <color rgb="00A9D18E"/>
+        <color rgb="FFA9D18E"/>
       </right>
       <top style="thin">
-        <color rgb="00A9D18E"/>
+        <color rgb="FFA9D18E"/>
       </top>
       <bottom style="thin">
-        <color rgb="00A9D18E"/>
+        <color rgb="FFA9D18E"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -297,8 +943,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BaseKeywords" displayName="BaseKeywords" ref="A1:B18" headerRowCount="1">
-  <autoFilter ref="A1:B18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="BaseKeywords" displayName="BaseKeywords" ref="A1:B28" headerRowCount="1">
+  <autoFilter ref="A1:B28"/>
   <tableColumns count="2">
     <tableColumn id="1" name="类别名称"/>
     <tableColumn id="2" name="关键词"/>
@@ -641,7 +1287,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -652,83 +1297,83 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="20.15" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>成本配置使用说明</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="14.15" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>1. 本文件由成本计算器读取。新增配置时，在对应工作表增加行或价格列。</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="14.15" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2. 不得修改工作表名称和固定表头，不得在数据区域合并单元格。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="14.15" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>3. 单价和优先级必须直接填写数字，不得使用 Excel 公式。</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="14.15" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4. 尺寸使用“数字*数字”格式，例如 50*160、120*40。</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="14.15" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>5. “基础商品价格”：类别名称和材质为行，尺寸为列；空白价格表示该组合未配置。新增尺寸时在最右侧增加尺寸列。</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7" ht="14.15" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>6. “枕芯价格”：尺寸和枕芯材质为行，六种枕芯类型为列；空白价格表示该组合未配置。PP棉会生成不带材质字样的枕芯关键词。</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8" ht="14.15" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>7. 修改后请保存并关闭本文件，再回到成本计算器点击“开始处理”。</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="9" ht="14.15" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>8. 基础商品新增类别时，需同时在“基础商品类别”“基础商品关键词”“基础商品价格”中添加相应内容。</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="10" ht="14.15" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>9. SSS 是当前正式材质关键词；本配置不包含起毛套成本。</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="11" ht="14.15" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>10. 全空行会被忽略；类别、材质或尺寸等固定字段留空会导致配置校验失败。</t>
         </is>
@@ -746,7 +1391,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="2"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -754,47 +1399,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>参数</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>值</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>配置版本</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>当前配置结构版本</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>代发单价</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="2" t="n">
         <v>5.5</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>每个枕芯、yr/义乳、yt/义臀产生的代发成本</t>
         </is>
@@ -815,61 +1460,61 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>类别名称</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>等身枕套</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -892,224 +1537,344 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>类别名称</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>分腿等身枕套</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>ft等身枕套</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>ft枕套</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>ft不开孔枕套</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>开胸开孔枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>kxkk枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>开孔开胸枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>kkkx枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>功能版枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>功能枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>开孔等身枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>kk等身枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>开孔枕套</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>开孔等身枕套</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>kk等身枕套</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>kk枕套</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>开胸等身枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>kx等身枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>开胸枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>kx枕套</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>等身枕套</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>等身枕套</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>等身枕套</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>枕套</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>防粉色</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>防深粉</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>防浅蓝</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>防蓝格</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>防尘套</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>防浅粉</t>
         </is>
@@ -1130,588 +1895,584 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>类别名称</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>材质</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>40*120</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>50*150</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>50*160</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>60*180</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>40*60</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>等身枕套</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>桃皮绒</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>等身枕套</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>短毛绒</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>等身枕套</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>2way</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="3" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>等身枕套</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>new2way</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="3" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>等身枕套</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>SSS</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="3" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>桃皮绒</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="G7" s="6" t="n"/>
+      <c r="G7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>短毛绒</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="G8" s="6" t="n"/>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>2way</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="G9" s="6" t="n"/>
+      <c r="G9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>new2way</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="G10" s="6" t="n"/>
+      <c r="G10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>开孔枕套</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>开孔/开胸/开孔开胸枕套</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>SSS</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="G11" s="6" t="n"/>
+      <c r="G11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>桃皮绒</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G12" s="5" t="n"/>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>短毛绒</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G13" s="5" t="n"/>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>2way</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="G14" s="5" t="n"/>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>new2way</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="G15" s="5" t="n"/>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>分腿枕套</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>SSS</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="G16" s="5" t="n"/>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>防粉色</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="G17" s="7" t="n"/>
+      <c r="G17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>防深粉</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="G18" s="7" t="n"/>
+      <c r="G18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>防浅蓝</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="G19" s="7" t="n"/>
+      <c r="G19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>防蓝格</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="G20" s="7" t="n"/>
+      <c r="G20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>防尘套</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="G21" s="7" t="n"/>
+      <c r="G21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>遮羞套</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>防浅粉</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="G22" s="7" t="n"/>
+      <c r="G22" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1734,297 +2495,290 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>尺寸</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>枕芯材质</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>标准等身</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>标准分腿</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>标准开孔</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>加重等身</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>加重分腿</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>加重开孔</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>120*40</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>PP棉</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="3" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>150*50</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>PP棉</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="3" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>160*50</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>PP棉</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="3" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>180*60</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>PP棉</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="3" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>120*40</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>羽绒棉</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="4" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>150*50</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>羽绒棉</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G7" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="4" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>160*50</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>羽绒棉</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="4" t="n">
         <v>58</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>180*60</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>羽绒棉</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="4" t="n">
         <v>65</v>
       </c>
     </row>
@@ -2049,111 +2803,111 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>二yr1500</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="2" t="n">
         <v>53</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>二yr1800</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="2" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>二yr2700</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="2" t="n">
         <v>92</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>三yr3250</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="2" t="n">
         <v>99</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>三yr1800</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="2" t="n">
         <v>69</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>yt2700</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="2" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>yt4100</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="2" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>四yr3100</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="2" t="n">
         <v>153</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>二yr2250</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="2" t="n">
         <v>56</v>
       </c>
     </row>
@@ -2177,41 +2931,41 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1" outlineLevelRow="2"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>关键词</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>硅胶</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>17.5</v>
+      <c r="B2" s="2" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>电动</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="2" t="n">
         <v>55</v>
       </c>
     </row>

--- a/成本配置模板.xlsx
+++ b/成本配置模板.xlsx
@@ -2554,22 +2554,22 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -2584,22 +2584,22 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -2614,22 +2614,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -2644,22 +2644,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
@@ -2674,22 +2674,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -2704,22 +2704,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -2734,22 +2734,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
@@ -2764,22 +2764,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
